--- a/SikaPay/merchants.xlsx
+++ b/SikaPay/merchants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Downloads/General Stuff Folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ludwi\Downloads\PythonProjects\SikaPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334F8BAA-3863-A64A-90EA-7A13C7CC3611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F95C736-B969-4D99-8689-C1C1363F2153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15980" xr2:uid="{2A099FC5-3976-7846-876C-9D8A7DE1F843}"/>
+    <workbookView xWindow="4230" yWindow="3645" windowWidth="15180" windowHeight="6780" xr2:uid="{2A099FC5-3976-7846-876C-9D8A7DE1F843}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Vendor ID</t>
-  </si>
-  <si>
     <t>Arhin's Bakeries</t>
   </si>
   <si>
@@ -71,6 +65,12 @@
   </si>
   <si>
     <t>Kara Cosmetics</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -135,9 +135,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +175,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -281,7 +281,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,7 +423,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -432,97 +432,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B2538B-1817-A14C-82A1-91F702F1D2B3}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>880931</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>556432</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>110088</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>554411</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>456732</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>550831</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>565644</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>232277</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>567833</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>660984</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
